--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -4892,7 +4892,7 @@
       </c>
       <c r="P16" s="35" t="inlineStr">
         <is>
-          <t>ataca em linha ou em área</t>
+          <t>ataca e empurra em linha ou em área</t>
         </is>
       </c>
     </row>

--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <name val="Roboto"/>
       <color rgb="00F4F1F7"/>
@@ -160,11 +160,6 @@
       <color rgb="00E8DCD4"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Roboto"/>
-      <color rgb="00998BA9"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -216,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -347,7 +342,13 @@
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -748,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AT120"/>
+  <dimension ref="A1:AT132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -811,7 +812,7 @@
       <c r="AE1" s="2" t="n"/>
       <c r="AF1" s="4" t="inlineStr">
         <is>
-          <t>capítulo 16 · Projeto - M</t>
+          <t>Capítulo 16 · Projeto - M</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1403,7 @@
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="16" t="inlineStr">
         <is>
-          <t>quantos corpos você põe em campo, quanta vida cada um tem, e o tamanho do orçamento</t>
+          <t>Quantos corpos você põe em campo, quanta vida cada um tem, e o tamanho do orçamento</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1425,7 @@
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>A Sintonia é a escolha de nível 2 do Evocador. Presa: crítico com 19 ou 20. Parrudo: mais vida, 5 × a sua maestria. Voz: sobe a CD dos efeitos dela — veja a seção 9.</t>
+          <t>A Sintonia é a escolha de nível 2 do Evocador. Presa: crítico com 19 ou 20. Parrudo: mais vida, 5 × a sua maestria. Voz: sobe a CD dos efeitos dela, e a seção 9 faz a conta.</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1747,7 @@
       </c>
       <c r="Y35" s="5" t="n"/>
       <c r="Z35" s="20">
-        <f>IF($D$30+$L$30+$T$30+$AB$30+$AJ$30&gt;(9+$D$11),"estourou o total",IF(MAX($D$30,$L$30,$T$30,$AB$30,$AJ$30)&gt;6,"estourou o teto de 6",IF($D$30+$L$30+$T$30+$AB$30+$AJ$30&lt;(9+$D$11),"sobrou ponto","ok")))</f>
+        <f>IF($D$30+$L$30+$T$30+$AB$30+$AJ$30&gt;(9+$D$11),"Estourou o total",IF(MAX($D$30,$L$30,$T$30,$AB$30,$AJ$30)&gt;6,"Estourou o teto de 6",IF($D$30+$L$30+$T$30+$AB$30+$AJ$30&lt;(9+$D$11),"Sobrou ponto","Ok")))</f>
         <v/>
       </c>
     </row>
@@ -2739,7 +2740,7 @@
       <c r="C68" s="5" t="n"/>
       <c r="D68" s="35" t="inlineStr">
         <is>
-          <t>quando um golpe só causar a régua inteira, ou quando o dano que passar de zero for maior que a metade da régua. A régua é a vida máxima dela. Área nunca destrói: ela derruba como qualquer dano. Fora desses dois casos ela só cai, e você reinvoca.</t>
+          <t>Quando um golpe só causar a régua inteira, ou quando o dano que passar de zero for maior que a metade da régua. A régua é a vida máxima dela. Área nunca destrói: ela derruba como qualquer dano. Fora desses dois casos ela só cai, e você reinvoca.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3500,7 @@
       </c>
       <c r="N92" s="5" t="n"/>
       <c r="O92" s="42">
-        <f>IF($D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)&lt;0,"estourou "&amp;(($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)-$D$76),$D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85))</f>
+        <f>IF($D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)&lt;0,"Estourou "&amp;(($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)-$D$76),$D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85))</f>
         <v/>
       </c>
       <c r="Y92" s="5" t="n"/>
@@ -3740,7 +3741,7 @@
       </c>
       <c r="N100" s="5" t="n"/>
       <c r="O100" s="21">
-        <f>IF($AK$19="Matilha","cada um dos cinco rola isto",IF($AK$19="","","o corpo em campo rola isto"))</f>
+        <f>IF($AK$19="Matilha","Cada um dos cinco rola isto",IF($AK$19="","","O corpo em campo rola isto"))</f>
         <v/>
       </c>
     </row>
@@ -3953,7 +3954,7 @@
         </is>
       </c>
       <c r="O108" s="44">
-        <f>("custa "&amp;$O$11&amp;" PE e a Ação Padrão")</f>
+        <f>("Custa "&amp;$O$11&amp;" PE e a Ação Padrão")</f>
         <v/>
       </c>
     </row>
@@ -3967,7 +3968,7 @@
         </is>
       </c>
       <c r="O109" s="45">
-        <f>"a Ação Padrão, toda rodada"</f>
+        <f>"A Ação Padrão, toda rodada"</f>
         <v/>
       </c>
     </row>
@@ -3981,7 +3982,7 @@
         </is>
       </c>
       <c r="O110" s="44">
-        <f>"a sua, e ela age logo depois de você"</f>
+        <f>"A sua, e ela age logo depois de você"</f>
         <v/>
       </c>
     </row>
@@ -4072,9 +4073,17 @@
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>O QUE A FICHA NÃO CALCULA</t>
-        </is>
-      </c>
+          <t>A CD DOS EFEITOS</t>
+        </is>
+      </c>
+      <c r="Y114" s="5" t="n"/>
+      <c r="Z114" s="5" t="n"/>
+      <c r="AA114" s="5" t="n"/>
+      <c r="AB114" s="5" t="n"/>
+      <c r="AC114" s="5" t="n"/>
+      <c r="AD114" s="5" t="n"/>
+      <c r="AE114" s="5" t="n"/>
+      <c r="AF114" s="5" t="n"/>
       <c r="AG114" s="5" t="n"/>
       <c r="AH114" s="5" t="n"/>
       <c r="AI114" s="5" t="n"/>
@@ -4139,9 +4148,27 @@
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="n"/>
       <c r="C116" s="5" t="n"/>
-      <c r="D116" s="34" t="inlineStr">
-        <is>
-          <t>A CD DOS EFEITOS DELA</t>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>ATRIBUTO DA MONTAGEM</t>
+        </is>
+      </c>
+      <c r="N116" s="5" t="n"/>
+      <c r="O116" s="8" t="inlineStr">
+        <is>
+          <t>PREITO NA CD (SERVO)</t>
+        </is>
+      </c>
+      <c r="Y116" s="5" t="n"/>
+      <c r="Z116" s="8" t="inlineStr">
+        <is>
+          <t>BÔNUS NA CD</t>
+        </is>
+      </c>
+      <c r="AJ116" s="5" t="n"/>
+      <c r="AK116" s="8" t="inlineStr">
+        <is>
+          <t>CD DOS EFEITOS</t>
         </is>
       </c>
     </row>
@@ -4149,8 +4176,17 @@
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="n"/>
       <c r="C117" s="5" t="n"/>
-      <c r="D117" s="35">
-        <f>IF($D$22="Voz","A Voz sobe a CD dos efeitos dela, e o sistema ainda não diz qual é essa CD. Combine com o mestre.","")</f>
+      <c r="D117" s="21" t="n"/>
+      <c r="N117" s="5" t="n"/>
+      <c r="O117" s="21" t="n"/>
+      <c r="Y117" s="5" t="n"/>
+      <c r="Z117" s="9">
+        <f>MAX(IF($D$22="Voz",IF($D$7&lt;7,1,MAX(1,FLOOR($AK$7/2,1))),0),IF(AND($AK$19="Servo",$O$117="sim"),MAX(1,FLOOR($AK$7/2,1)),0))</f>
+        <v/>
+      </c>
+      <c r="AJ117" s="5" t="n"/>
+      <c r="AK117" s="9">
+        <f>IF($D$117="","",8+INDEX(DADOS!$AK$3:$AK$7,MATCH($D$117,DADOS!$C$2:$C$6,0))+$AK$7+$Z$117)</f>
         <v/>
       </c>
     </row>
@@ -4158,53 +4194,67 @@
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="n"/>
       <c r="C118" s="5" t="n"/>
-      <c r="D118" s="46" t="inlineStr">
-        <is>
-          <t>A CD dos efeitos dela não tem fórmula em documento nenhum — nem o capítulo 16, nem a peça 15 escrevem uma. Enquanto não existir, combine o número com o mestre.</t>
-        </is>
-      </c>
+      <c r="N118" s="5" t="n"/>
+      <c r="Y118" s="5" t="n"/>
+      <c r="AJ118" s="5" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="n"/>
       <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="5" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="5" t="n"/>
+      <c r="I119" s="5" t="n"/>
+      <c r="J119" s="5" t="n"/>
+      <c r="K119" s="5" t="n"/>
+      <c r="L119" s="5" t="n"/>
+      <c r="M119" s="5" t="n"/>
+      <c r="N119" s="5" t="n"/>
+      <c r="O119" s="5" t="n"/>
+      <c r="P119" s="5" t="n"/>
+      <c r="Q119" s="5" t="n"/>
+      <c r="R119" s="5" t="n"/>
+      <c r="S119" s="5" t="n"/>
+      <c r="T119" s="5" t="n"/>
+      <c r="U119" s="5" t="n"/>
+      <c r="V119" s="5" t="n"/>
+      <c r="W119" s="5" t="n"/>
+      <c r="X119" s="5" t="n"/>
+      <c r="Y119" s="5" t="n"/>
+      <c r="Z119" s="5" t="n"/>
+      <c r="AA119" s="5" t="n"/>
+      <c r="AB119" s="5" t="n"/>
+      <c r="AC119" s="5" t="n"/>
+      <c r="AD119" s="5" t="n"/>
+      <c r="AE119" s="5" t="n"/>
+      <c r="AF119" s="5" t="n"/>
+      <c r="AG119" s="5" t="n"/>
+      <c r="AH119" s="5" t="n"/>
+      <c r="AI119" s="5" t="n"/>
+      <c r="AJ119" s="5" t="n"/>
+      <c r="AK119" s="5" t="n"/>
+      <c r="AL119" s="5" t="n"/>
+      <c r="AM119" s="5" t="n"/>
+      <c r="AN119" s="5" t="n"/>
+      <c r="AO119" s="5" t="n"/>
+      <c r="AP119" s="5" t="n"/>
+      <c r="AQ119" s="5" t="n"/>
+      <c r="AR119" s="5" t="n"/>
+      <c r="AS119" s="5" t="n"/>
+      <c r="AT119" s="5" t="n"/>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="1" t="n"/>
       <c r="B120" s="1" t="n"/>
       <c r="C120" s="5" t="n"/>
-      <c r="D120" s="5" t="n"/>
-      <c r="E120" s="5" t="n"/>
-      <c r="F120" s="5" t="n"/>
-      <c r="G120" s="5" t="n"/>
-      <c r="H120" s="5" t="n"/>
-      <c r="I120" s="5" t="n"/>
-      <c r="J120" s="5" t="n"/>
-      <c r="K120" s="5" t="n"/>
-      <c r="L120" s="5" t="n"/>
-      <c r="M120" s="5" t="n"/>
-      <c r="N120" s="5" t="n"/>
-      <c r="O120" s="5" t="n"/>
-      <c r="P120" s="5" t="n"/>
-      <c r="Q120" s="5" t="n"/>
-      <c r="R120" s="5" t="n"/>
-      <c r="S120" s="5" t="n"/>
-      <c r="T120" s="5" t="n"/>
-      <c r="U120" s="5" t="n"/>
-      <c r="V120" s="5" t="n"/>
-      <c r="W120" s="5" t="n"/>
-      <c r="X120" s="5" t="n"/>
-      <c r="Y120" s="5" t="n"/>
-      <c r="Z120" s="5" t="n"/>
-      <c r="AA120" s="5" t="n"/>
-      <c r="AB120" s="5" t="n"/>
-      <c r="AC120" s="5" t="n"/>
-      <c r="AD120" s="5" t="n"/>
-      <c r="AE120" s="5" t="n"/>
-      <c r="AF120" s="5" t="n"/>
-      <c r="AG120" s="5" t="n"/>
-      <c r="AH120" s="5" t="n"/>
-      <c r="AI120" s="5" t="n"/>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>CONFERÊNCIA</t>
+        </is>
+      </c>
       <c r="AJ120" s="5" t="n"/>
       <c r="AK120" s="5" t="n"/>
       <c r="AL120" s="5" t="n"/>
@@ -4217,8 +4267,55 @@
       <c r="AS120" s="5" t="n"/>
       <c r="AT120" s="5" t="n"/>
     </row>
+    <row r="121">
+      <c r="D121" s="20">
+        <f>IF($D$117="","Escolha o atributo da montagem",IF(AND($O$117="sim",$AK$19&lt;&gt;"Servo"),"O Preito é do Servo",IF(AND($D$43&lt;&gt;"",$D$43&lt;&gt;$D$117),"O acerto usa outro atributo: só vale com arma","Ok")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123">
+      <c r="D123" s="46" t="inlineStr">
+        <is>
+          <t>CD = 8 + o atributo da montagem + a maestria do dono + o bônus. O acerto e a CD saem do mesmo atributo, e a escolha não muda depois; só o acerto muda se ela empunhar uma arma, e a CD fica neste atributo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124"/>
+    <row r="125">
+      <c r="D125" s="46" t="inlineStr">
+        <is>
+          <t>A Voz (Sintonia) e o Preito do Servo na CD não somam: dão o mesmo número em todo nível, e a planilha leva um só. Marque o Preito aqui só se o Servo escolheu a CD nele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126"/>
+    <row r="127">
+      <c r="D127" s="47" t="inlineStr">
+        <is>
+          <t>O alvo rola contra essa CD: Fisgada · Agarrar · Arrastar · Jorro (Físico); Chamariz (Espírito). O Graúdo não pede rolagem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128"/>
+    <row r="129">
+      <c r="D129" s="48" t="inlineStr">
+        <is>
+          <t>O QUE A FICHA NÃO CALCULA</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="D130" s="35" t="inlineStr">
+        <is>
+          <t>Invocação com arma: o livro ainda não diz quem treina a invocação numa arma, nem se o dado da arma soma ao Investir. Combine com o mestre. O Preito também soma nas perícias e nos Testes de Resistência dela, e pode somar no acerto ou na Defesa: use o Extra dos Testes de Resistência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131"/>
+    <row r="132"/>
   </sheetData>
-  <mergeCells count="198">
+  <mergeCells count="210">
     <mergeCell ref="AK84:AN84"/>
     <mergeCell ref="D59:M60"/>
     <mergeCell ref="AB30:AH31"/>
@@ -4245,6 +4342,7 @@
     <mergeCell ref="O108:AT108"/>
     <mergeCell ref="O10:X10"/>
     <mergeCell ref="AH50:AL50"/>
+    <mergeCell ref="Z117:AI118"/>
     <mergeCell ref="A8:B26"/>
     <mergeCell ref="Z49:AF49"/>
     <mergeCell ref="AK19:AT19"/>
@@ -4282,19 +4380,23 @@
     <mergeCell ref="AJ29:AP29"/>
     <mergeCell ref="Z19:AI19"/>
     <mergeCell ref="D29:J29"/>
+    <mergeCell ref="AK117:AT118"/>
     <mergeCell ref="AK80:AN80"/>
     <mergeCell ref="G27:AF27"/>
     <mergeCell ref="S86:W86"/>
     <mergeCell ref="D70:AT71"/>
     <mergeCell ref="D27:F28"/>
     <mergeCell ref="L30:R31"/>
+    <mergeCell ref="G114:X114"/>
     <mergeCell ref="L32:R32"/>
     <mergeCell ref="T29:Z29"/>
     <mergeCell ref="D110:N110"/>
     <mergeCell ref="AO83:AS83"/>
+    <mergeCell ref="D120:AI120"/>
     <mergeCell ref="O112:AT112"/>
     <mergeCell ref="D46:M46"/>
     <mergeCell ref="G16:X16"/>
+    <mergeCell ref="O116:X116"/>
     <mergeCell ref="AB32:AH32"/>
     <mergeCell ref="Z83:AJ83"/>
     <mergeCell ref="Z34:AT34"/>
@@ -4304,6 +4406,8 @@
     <mergeCell ref="D21:M21"/>
     <mergeCell ref="L50:P50"/>
     <mergeCell ref="G97:AB97"/>
+    <mergeCell ref="D117:M118"/>
+    <mergeCell ref="Z116:AI116"/>
     <mergeCell ref="D49:J49"/>
     <mergeCell ref="AO84:AS84"/>
     <mergeCell ref="O21:AT21"/>
@@ -4316,7 +4420,6 @@
     <mergeCell ref="O43:X43"/>
     <mergeCell ref="D89:AT90"/>
     <mergeCell ref="S88:W88"/>
-    <mergeCell ref="D116:AT116"/>
     <mergeCell ref="Z51:AF51"/>
     <mergeCell ref="AK81:AN81"/>
     <mergeCell ref="D79:N79"/>
@@ -4327,12 +4430,14 @@
     <mergeCell ref="S81:W81"/>
     <mergeCell ref="D58:M58"/>
     <mergeCell ref="D81:N81"/>
+    <mergeCell ref="O117:X118"/>
     <mergeCell ref="O85:R85"/>
     <mergeCell ref="AK6:AT6"/>
     <mergeCell ref="D42:M42"/>
     <mergeCell ref="D76:M77"/>
     <mergeCell ref="D35:M35"/>
     <mergeCell ref="Z65:AI65"/>
+    <mergeCell ref="D130:AT132"/>
     <mergeCell ref="S82:W82"/>
     <mergeCell ref="D40:F41"/>
     <mergeCell ref="G40:AH40"/>
@@ -4342,6 +4447,7 @@
     <mergeCell ref="D18:X18"/>
     <mergeCell ref="Q50:U50"/>
     <mergeCell ref="D99:M99"/>
+    <mergeCell ref="D129:AT129"/>
     <mergeCell ref="T32:Z32"/>
     <mergeCell ref="AB29:AH29"/>
     <mergeCell ref="O6:X6"/>
@@ -4359,13 +4465,14 @@
     <mergeCell ref="O7:X8"/>
     <mergeCell ref="D24:AT25"/>
     <mergeCell ref="D32:J32"/>
-    <mergeCell ref="G114:AF114"/>
     <mergeCell ref="D83:N83"/>
     <mergeCell ref="Z59:AI60"/>
     <mergeCell ref="AM50:AQ50"/>
+    <mergeCell ref="D121:AI121"/>
     <mergeCell ref="A30:B48"/>
     <mergeCell ref="D85:N85"/>
     <mergeCell ref="Z84:AJ84"/>
+    <mergeCell ref="D123:AT124"/>
     <mergeCell ref="O58:X58"/>
     <mergeCell ref="O11:X11"/>
     <mergeCell ref="Z7:AI8"/>
@@ -4376,7 +4483,6 @@
     <mergeCell ref="Z46:AI46"/>
     <mergeCell ref="O22:AT23"/>
     <mergeCell ref="D50:J50"/>
-    <mergeCell ref="D117:AT117"/>
     <mergeCell ref="Q51:U51"/>
     <mergeCell ref="Z81:AJ81"/>
     <mergeCell ref="O34:X34"/>
@@ -4384,6 +4490,7 @@
     <mergeCell ref="AK82:AN82"/>
     <mergeCell ref="D10:M10"/>
     <mergeCell ref="O59:X60"/>
+    <mergeCell ref="AK116:AT116"/>
     <mergeCell ref="O100:AT101"/>
     <mergeCell ref="AN49:AT49"/>
     <mergeCell ref="AK59:AT60"/>
@@ -4391,6 +4498,7 @@
     <mergeCell ref="O92:X92"/>
     <mergeCell ref="O99:AT99"/>
     <mergeCell ref="O45:X45"/>
+    <mergeCell ref="D125:AT126"/>
     <mergeCell ref="AK83:AN83"/>
     <mergeCell ref="D4:F5"/>
     <mergeCell ref="Z50:AF50"/>
@@ -4401,8 +4509,9 @@
     <mergeCell ref="D11:M11"/>
     <mergeCell ref="O65:X65"/>
     <mergeCell ref="S83:W83"/>
-    <mergeCell ref="D118:AT119"/>
+    <mergeCell ref="D116:M116"/>
     <mergeCell ref="D97:F98"/>
+    <mergeCell ref="D127:AT128"/>
     <mergeCell ref="O84:R84"/>
     <mergeCell ref="D30:J31"/>
     <mergeCell ref="D106:F107"/>
@@ -4418,7 +4527,7 @@
     <mergeCell ref="AO85:AS85"/>
     <mergeCell ref="O80:R80"/>
   </mergeCells>
-  <dataValidations count="37">
+  <dataValidations count="39">
     <dataValidation sqref="Z19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$A$2:$A$5</formula1>
     </dataValidation>
@@ -4530,6 +4639,12 @@
     <dataValidation sqref="AK85:AN85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
       <formula1>DADOS!$AQ$2:$AQ$5</formula1>
     </dataValidation>
+    <dataValidation sqref="D117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="O117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"sim"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
@@ -4597,7 +4712,7 @@
       <c r="A1" s="5" t="n"/>
       <c r="B1" s="5" t="n"/>
       <c r="C1" s="2" t="n"/>
-      <c r="D1" s="47" t="inlineStr">
+      <c r="D1" s="49" t="inlineStr">
         <is>
           <t>O CATÁLOGO — o que dá para comprar</t>
         </is>
@@ -4605,7 +4720,7 @@
       <c r="AE1" s="2" t="n"/>
       <c r="AF1" s="4" t="inlineStr">
         <is>
-          <t>capítulo 16</t>
+          <t>Capítulo 16</t>
         </is>
       </c>
     </row>
@@ -4667,14 +4782,14 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>TRAÇO</t>
         </is>
       </c>
-      <c r="U4" s="49" t="inlineStr">
-        <is>
-          <t>o corpo dela. Vale sempre, sem gastar ação.</t>
+      <c r="U4" s="51" t="inlineStr">
+        <is>
+          <t>O corpo dela. Vale sempre, sem gastar ação.</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4817,7 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="50" t="n">
+      <c r="D6" s="52" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="25" t="inlineStr">
@@ -4712,7 +4827,7 @@
       </c>
       <c r="P6" s="35" t="inlineStr">
         <is>
-          <t>sobe parede e teto sem teste</t>
+          <t>Sobe parede e teto sem teste</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4835,7 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="51" t="n">
+      <c r="D7" s="53" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="29" t="inlineStr">
@@ -4728,9 +4843,9 @@
           <t>Nado</t>
         </is>
       </c>
-      <c r="P7" s="52" t="inlineStr">
-        <is>
-          <t>move na água sem penalidade. Rio, cisterna, tanque alagado de estação</t>
+      <c r="P7" s="54" t="inlineStr">
+        <is>
+          <t>Move na água sem penalidade. Rio, cisterna, tanque alagado de estação</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4853,7 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="50" t="n">
+      <c r="D8" s="52" t="n">
         <v>3</v>
       </c>
       <c r="H8" s="25" t="inlineStr">
@@ -4748,7 +4863,7 @@
       </c>
       <c r="P8" s="35" t="inlineStr">
         <is>
-          <t>ela fala, e dá para conversar com ela</t>
+          <t>Ela fala, e dá para conversar com ela</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4871,7 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="51" t="n">
+      <c r="D9" s="53" t="n">
         <v>5</v>
       </c>
       <c r="H9" s="29" t="inlineStr">
@@ -4764,9 +4879,9 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="P9" s="52" t="inlineStr">
-        <is>
-          <t>rastreia por cheiro e por energia. Pega rastro velho de horas</t>
+      <c r="P9" s="54" t="inlineStr">
+        <is>
+          <t>Rastreia por cheiro e por energia. Pega rastro velho de horas</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4889,7 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="50" t="n">
+      <c r="D10" s="52" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="25" t="inlineStr">
@@ -4784,7 +4899,7 @@
       </c>
       <c r="P10" s="35" t="inlineStr">
         <is>
-          <t>o que ela vê e ouve, você vê e ouve também</t>
+          <t>O que ela vê e ouve, você vê e ouve também</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4907,7 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="51" t="n">
+      <c r="D11" s="53" t="n">
         <v>7</v>
       </c>
       <c r="H11" s="29" t="inlineStr">
@@ -4800,9 +4915,9 @@
           <t>Miúdo</t>
         </is>
       </c>
-      <c r="P11" s="52" t="inlineStr">
-        <is>
-          <t>ocupa espaço menor e passa por vão. Duto, grade de bueiro, folga embaixo da porta</t>
+      <c r="P11" s="54" t="inlineStr">
+        <is>
+          <t>Ocupa espaço menor e passa por vão. Duto, grade de bueiro, folga embaixo da porta</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4925,7 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="50" t="n">
+      <c r="D12" s="52" t="n">
         <v>8</v>
       </c>
       <c r="H12" s="25" t="inlineStr">
@@ -4820,7 +4935,7 @@
       </c>
       <c r="P12" s="35" t="inlineStr">
         <is>
-          <t>o deslocamento dela passa a ser de voo também</t>
+          <t>O deslocamento dela passa a ser de voo também</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4943,7 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="51" t="n">
+      <c r="D13" s="53" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="29" t="inlineStr">
@@ -4836,9 +4951,9 @@
           <t>Montaria</t>
         </is>
       </c>
-      <c r="P13" s="52" t="inlineStr">
-        <is>
-          <t>carrega uma pessoa ou mais, dependendo do tamanho</t>
+      <c r="P13" s="54" t="inlineStr">
+        <is>
+          <t>Carrega uma pessoa ou mais, dependendo do tamanho</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4961,7 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="50" t="n">
+      <c r="D14" s="52" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="25" t="inlineStr">
@@ -4856,7 +4971,7 @@
       </c>
       <c r="P14" s="35" t="inlineStr">
         <is>
-          <t>prende à distância. Ela alcança, engancha, e quem ia fugir para de conseguir</t>
+          <t>Prende à distância. Ela alcança, engancha, e quem ia fugir para de conseguir</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4979,7 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="51" t="n">
+      <c r="D15" s="53" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="29" t="inlineStr">
@@ -4872,9 +4987,9 @@
           <t>Emboscada</t>
         </is>
       </c>
-      <c r="P15" s="52" t="inlineStr">
-        <is>
-          <t>surge do chão, fora do alcance de visão</t>
+      <c r="P15" s="54" t="inlineStr">
+        <is>
+          <t>Surge do chão, fora do alcance de visão</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4997,7 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="50" t="n">
+      <c r="D16" s="52" t="n">
         <v>8</v>
       </c>
       <c r="H16" s="25" t="inlineStr">
@@ -4892,7 +5007,7 @@
       </c>
       <c r="P16" s="35" t="inlineStr">
         <is>
-          <t>ataca e empurra em linha ou em área</t>
+          <t>Ataca e empurra em linha ou em área</t>
         </is>
       </c>
     </row>
@@ -4900,7 +5015,7 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="51" t="n">
+      <c r="D17" s="53" t="n">
         <v>8</v>
       </c>
       <c r="H17" s="29" t="inlineStr">
@@ -4908,9 +5023,9 @@
           <t>Graúdo</t>
         </is>
       </c>
-      <c r="P17" s="52" t="inlineStr">
-        <is>
-          <t>ocupa espaço maior e barra passagem</t>
+      <c r="P17" s="54" t="inlineStr">
+        <is>
+          <t>Ocupa espaço maior e barra passagem</t>
         </is>
       </c>
     </row>
@@ -4918,7 +5033,7 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="50" t="n">
+      <c r="D18" s="52" t="n">
         <v>8</v>
       </c>
       <c r="H18" s="25" t="inlineStr">
@@ -4928,7 +5043,7 @@
       </c>
       <c r="P18" s="35" t="inlineStr">
         <is>
-          <t>funciona além dos 18 metros da amarra. Dentro da cena, para qualquer um; fora da cena, com requisito</t>
+          <t>Funciona além dos 18 metros da amarra. Dentro da cena, para qualquer um; fora da cena, com requisito</t>
         </is>
       </c>
     </row>
@@ -5032,14 +5147,14 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="48" t="inlineStr">
+      <c r="D21" s="50" t="inlineStr">
         <is>
           <t>COMANDO</t>
         </is>
       </c>
-      <c r="U21" s="49" t="inlineStr">
-        <is>
-          <t>o que ela faz quando você gasta a Ação Padrão comandando.</t>
+      <c r="U21" s="51" t="inlineStr">
+        <is>
+          <t>O que ela faz quando você gasta a Ação Padrão comandando.</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5182,7 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
-      <c r="D23" s="50" t="n">
+      <c r="D23" s="52" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="25" t="inlineStr">
@@ -5077,7 +5192,7 @@
       </c>
       <c r="P23" s="35" t="inlineStr">
         <is>
-          <t>o ataque. Toda invocação tem</t>
+          <t>O ataque. Toda invocação tem</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5200,7 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="51" t="n">
+      <c r="D24" s="53" t="n">
         <v>4</v>
       </c>
       <c r="H24" s="29" t="inlineStr">
@@ -5093,9 +5208,9 @@
           <t>Agarrar</t>
         </is>
       </c>
-      <c r="P24" s="52" t="inlineStr">
-        <is>
-          <t>prende o alvo</t>
+      <c r="P24" s="54" t="inlineStr">
+        <is>
+          <t>Prende o alvo</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5218,7 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
-      <c r="D25" s="50" t="n">
+      <c r="D25" s="52" t="n">
         <v>4</v>
       </c>
       <c r="H25" s="25" t="inlineStr">
@@ -5113,7 +5228,7 @@
       </c>
       <c r="P25" s="35" t="inlineStr">
         <is>
-          <t>move o alvo, ou se move levando ele. Tira alguém de cima de uma beirada, ou põe</t>
+          <t>Move o alvo, ou se move levando ele. Tira alguém de cima de uma beirada, ou põe</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5236,7 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="51" t="n">
+      <c r="D26" s="53" t="n">
         <v>4</v>
       </c>
       <c r="H26" s="29" t="inlineStr">
@@ -5129,9 +5244,9 @@
           <t>Buscar</t>
         </is>
       </c>
-      <c r="P26" s="52" t="inlineStr">
-        <is>
-          <t>pega um objeto, ou rastreia de forma ativa</t>
+      <c r="P26" s="54" t="inlineStr">
+        <is>
+          <t>Pega um objeto, ou rastreia de forma ativa</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5254,7 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
-      <c r="D27" s="50" t="n">
+      <c r="D27" s="52" t="n">
         <v>4</v>
       </c>
       <c r="H27" s="25" t="inlineStr">
@@ -5149,7 +5264,7 @@
       </c>
       <c r="P27" s="35" t="inlineStr">
         <is>
-          <t>abre buraco, desenterra, revira o terreno. Faz rota onde não havia rota</t>
+          <t>Abre buraco, desenterra, revira o terreno. Faz rota onde não havia rota</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5272,7 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="5" t="n"/>
-      <c r="D28" s="51" t="n">
+      <c r="D28" s="53" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="29" t="inlineStr">
@@ -5165,9 +5280,9 @@
           <t>Interpor</t>
         </is>
       </c>
-      <c r="P28" s="52" t="inlineStr">
-        <is>
-          <t>se põe entre você e o golpe. O corpo dela recebe o que ia em você</t>
+      <c r="P28" s="54" t="inlineStr">
+        <is>
+          <t>Se põe entre você e o golpe. O corpo dela recebe o que ia em você</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5290,7 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="50" t="n">
+      <c r="D29" s="52" t="n">
         <v>8</v>
       </c>
       <c r="H29" s="25" t="inlineStr">
@@ -5185,7 +5300,7 @@
       </c>
       <c r="P29" s="35" t="inlineStr">
         <is>
-          <t>o alvo tem de vir para cima dela. Você escolhe em quem a coisa está prestando atenção</t>
+          <t>O alvo tem de vir para cima dela. Você escolhe em quem a coisa está prestando atenção</t>
         </is>
       </c>
     </row>
@@ -5289,14 +5404,14 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
-      <c r="D32" s="48" t="inlineStr">
+      <c r="D32" s="50" t="inlineStr">
         <is>
           <t>INVENTAR O SEU</t>
         </is>
       </c>
-      <c r="U32" s="49" t="inlineStr">
-        <is>
-          <t>escreva o efeito, ache na régua o preço, e leve para o mestre aprovar</t>
+      <c r="U32" s="51" t="inlineStr">
+        <is>
+          <t>Escreva o efeito, ache na régua o preço, e leve para o mestre aprovar</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5421,7 @@
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>régua de TRAÇO</t>
+          <t>Régua de TRAÇO</t>
         </is>
       </c>
     </row>
@@ -5314,12 +5429,12 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
-      <c r="D34" s="50" t="n">
+      <c r="D34" s="52" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="35" t="inlineStr">
         <is>
-          <t>muda como ela anda, e só ela</t>
+          <t>Muda como ela anda, e só ela</t>
         </is>
       </c>
     </row>
@@ -5327,12 +5442,12 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
-      <c r="D35" s="51" t="n">
+      <c r="D35" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="52" t="inlineStr">
-        <is>
-          <t>muda o que ela comunica</t>
+      <c r="H35" s="54" t="inlineStr">
+        <is>
+          <t>Muda o que ela comunica</t>
         </is>
       </c>
     </row>
@@ -5340,12 +5455,12 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
-      <c r="D36" s="50" t="n">
+      <c r="D36" s="52" t="n">
         <v>5</v>
       </c>
       <c r="H36" s="35" t="inlineStr">
         <is>
-          <t>muda o que ela percebe</t>
+          <t>Muda o que ela percebe</t>
         </is>
       </c>
     </row>
@@ -5353,12 +5468,12 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
-      <c r="D37" s="51" t="n">
+      <c r="D37" s="53" t="n">
         <v>7</v>
       </c>
-      <c r="H37" s="52" t="inlineStr">
-        <is>
-          <t>muda que espaço ela ocupa, a um passo de mexer no tabuleiro</t>
+      <c r="H37" s="54" t="inlineStr">
+        <is>
+          <t>Muda que espaço ela ocupa, a um passo de mexer no tabuleiro</t>
         </is>
       </c>
     </row>
@@ -5366,12 +5481,12 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="n"/>
-      <c r="D38" s="50" t="n">
+      <c r="D38" s="52" t="n">
         <v>8</v>
       </c>
       <c r="H38" s="35" t="inlineStr">
         <is>
-          <t>encosta em outra criatura ou no ambiente: carrega, prende, empurra, barra, alcança além do alcance, aparece onde não dava</t>
+          <t>Encosta em outra criatura ou no ambiente: carrega, prende, empurra, barra, alcança além do alcance, aparece onde não dava</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5544,7 @@
       <c r="C40" s="5" t="n"/>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t>régua de COMANDO</t>
+          <t>Régua de COMANDO</t>
         </is>
       </c>
     </row>
@@ -5437,12 +5552,12 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
-      <c r="D41" s="50" t="n">
+      <c r="D41" s="52" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="35" t="inlineStr">
         <is>
-          <t>é o ataque</t>
+          <t>É o ataque</t>
         </is>
       </c>
     </row>
@@ -5450,12 +5565,12 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
-      <c r="D42" s="51" t="n">
+      <c r="D42" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="H42" s="52" t="inlineStr">
-        <is>
-          <t>faz uma coisa com um alvo ou um objeto</t>
+      <c r="H42" s="54" t="inlineStr">
+        <is>
+          <t>Faz uma coisa com um alvo ou um objeto</t>
         </is>
       </c>
     </row>
@@ -5463,12 +5578,12 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
-      <c r="D43" s="50" t="n">
+      <c r="D43" s="52" t="n">
         <v>8</v>
       </c>
       <c r="H43" s="35" t="inlineStr">
         <is>
-          <t>protege você, ou nega a ação de outro</t>
+          <t>Protege você, ou nega a ação de outro</t>
         </is>
       </c>
     </row>
@@ -5536,12 +5651,12 @@
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>dado de dano</t>
-        </is>
-      </c>
-      <c r="R46" s="53" t="inlineStr">
-        <is>
-          <t>o teto de uma Rotina já governa a saída. Um Traço que dê +1d6 não existe</t>
+          <t>Dado de dano</t>
+        </is>
+      </c>
+      <c r="R46" s="55" t="inlineStr">
+        <is>
+          <t>O teto de uma Rotina já governa a saída. Um Traço que dê +1d6 não existe</t>
         </is>
       </c>
     </row>
@@ -5551,12 +5666,12 @@
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="29" t="inlineStr">
         <is>
-          <t>qualquer coisa que cresça com refino</t>
-        </is>
-      </c>
-      <c r="R47" s="54" t="inlineStr">
-        <is>
-          <t>refino cresce muito mais rápido que a ficha dela, e ela passaria de você</t>
+          <t>Qualquer coisa que cresça com refino</t>
+        </is>
+      </c>
+      <c r="R47" s="56" t="inlineStr">
+        <is>
+          <t>Refino cresce muito mais rápido que a ficha dela, e ela passaria de você</t>
         </is>
       </c>
     </row>
@@ -5566,12 +5681,12 @@
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>atributo</t>
-        </is>
-      </c>
-      <c r="R48" s="53" t="inlineStr">
-        <is>
-          <t>os cinco já saem do arranjo dela, e comprar de novo é pagar duas vezes</t>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="R48" s="55" t="inlineStr">
+        <is>
+          <t>Os cinco já saem do arranjo dela, e comprar de novo é pagar duas vezes</t>
         </is>
       </c>
     </row>
@@ -5584,9 +5699,9 @@
           <t>Defesa, acerto ou vida direto</t>
         </is>
       </c>
-      <c r="R49" s="54" t="inlineStr">
-        <is>
-          <t>os três saem dos atributos dela</t>
+      <c r="R49" s="56" t="inlineStr">
+        <is>
+          <t>Os três saem dos atributos dela</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR92"/>
+  <dimension ref="A1:AR96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6464,60 +6579,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>tipos</t>
         </is>
       </c>
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>trilhas</t>
         </is>
       </c>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>atributos</t>
         </is>
       </c>
-      <c r="D1" s="55" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>trs</t>
         </is>
       </c>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>sintonia</t>
         </is>
       </c>
-      <c r="F1" s="55" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="G1" s="55" t="inlineStr">
+      <c r="G1" s="57" t="inlineStr">
         <is>
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="H1" s="55" t="inlineStr">
+      <c r="H1" s="57" t="inlineStr">
         <is>
           <t>traco</t>
         </is>
       </c>
-      <c r="I1" s="55" t="inlineStr">
+      <c r="I1" s="57" t="inlineStr">
         <is>
           <t>comando</t>
         </is>
       </c>
       <c r="J1" s="5" t="n"/>
-      <c r="K1" s="55" t="inlineStr">
+      <c r="K1" s="57" t="inlineStr">
         <is>
           <t>tab_tipos</t>
         </is>
       </c>
       <c r="L1" s="5" t="n"/>
       <c r="M1" s="5" t="n"/>
-      <c r="N1" s="55" t="inlineStr">
+      <c r="N1" s="57" t="inlineStr">
         <is>
           <t>tab_trilhas</t>
         </is>
@@ -6527,21 +6642,21 @@
       <c r="Q1" s="5" t="n"/>
       <c r="R1" s="5" t="n"/>
       <c r="S1" s="5" t="n"/>
-      <c r="T1" s="55" t="inlineStr">
+      <c r="T1" s="57" t="inlineStr">
         <is>
           <t>tab_traco</t>
         </is>
       </c>
       <c r="U1" s="5" t="n"/>
       <c r="V1" s="5" t="n"/>
-      <c r="W1" s="55" t="inlineStr">
+      <c r="W1" s="57" t="inlineStr">
         <is>
           <t>tab_comando</t>
         </is>
       </c>
       <c r="X1" s="5" t="n"/>
       <c r="Y1" s="5" t="n"/>
-      <c r="Z1" s="55" t="inlineStr">
+      <c r="Z1" s="57" t="inlineStr">
         <is>
           <t>tab_investir</t>
         </is>
@@ -6549,7 +6664,7 @@
       <c r="AA1" s="5" t="n"/>
       <c r="AB1" s="5" t="n"/>
       <c r="AC1" s="5" t="n"/>
-      <c r="AD1" s="55" t="inlineStr">
+      <c r="AD1" s="57" t="inlineStr">
         <is>
           <t>tab_trs</t>
         </is>
@@ -6565,12 +6680,12 @@
       <c r="AM1" s="5" t="n"/>
       <c r="AN1" s="5" t="n"/>
       <c r="AO1" s="5" t="n"/>
-      <c r="AP1" s="55" t="inlineStr">
+      <c r="AP1" s="57" t="inlineStr">
         <is>
           <t>degrau_traco</t>
         </is>
       </c>
-      <c r="AQ1" s="55" t="inlineStr">
+      <c r="AQ1" s="57" t="inlineStr">
         <is>
           <t>degrau_comando</t>
         </is>
@@ -6578,47 +6693,47 @@
       <c r="AR1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="56" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>talismã</t>
         </is>
       </c>
-      <c r="B2" s="56" t="inlineStr">
+      <c r="B2" s="58" t="inlineStr">
         <is>
           <t>Servo</t>
         </is>
       </c>
-      <c r="C2" s="56" t="inlineStr">
+      <c r="C2" s="58" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
       </c>
-      <c r="D2" s="56" t="inlineStr">
+      <c r="D2" s="58" t="inlineStr">
         <is>
           <t>Físico</t>
         </is>
       </c>
-      <c r="E2" s="56" t="inlineStr">
+      <c r="E2" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F2" s="56" t="inlineStr">
+      <c r="F2" s="58" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
       </c>
-      <c r="G2" s="56" t="inlineStr">
+      <c r="G2" s="58" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
       </c>
-      <c r="H2" s="56" t="inlineStr">
+      <c r="H2" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I2" s="56" t="inlineStr">
+      <c r="I2" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6743,12 +6858,12 @@
         </is>
       </c>
       <c r="AO2" s="5" t="n"/>
-      <c r="AP2" s="56" t="inlineStr">
+      <c r="AP2" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AQ2" s="56" t="inlineStr">
+      <c r="AQ2" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6756,434 +6871,434 @@
       <c r="AR2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="56" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>corpo amaldiçoado</t>
         </is>
       </c>
-      <c r="B3" s="56" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>Matilha</t>
         </is>
       </c>
-      <c r="C3" s="56" t="inlineStr">
+      <c r="C3" s="58" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
       </c>
-      <c r="D3" s="56" t="inlineStr">
+      <c r="D3" s="58" t="inlineStr">
         <is>
           <t>Vigor</t>
         </is>
       </c>
-      <c r="E3" s="56" t="inlineStr">
+      <c r="E3" s="58" t="inlineStr">
         <is>
           <t>Presa</t>
         </is>
       </c>
-      <c r="F3" s="56" t="inlineStr">
+      <c r="F3" s="58" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
       </c>
-      <c r="G3" s="56" t="inlineStr">
+      <c r="G3" s="58" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
       </c>
-      <c r="H3" s="56" t="inlineStr">
+      <c r="H3" s="58" t="inlineStr">
         <is>
           <t>Escalada</t>
         </is>
       </c>
-      <c r="I3" s="56" t="inlineStr">
+      <c r="I3" s="58" t="inlineStr">
         <is>
           <t>Investir</t>
         </is>
       </c>
       <c r="J3" s="5" t="n"/>
-      <c r="K3" s="56" t="inlineStr">
+      <c r="K3" s="58" t="inlineStr">
         <is>
           <t>talismã</t>
         </is>
       </c>
-      <c r="L3" s="56" t="n">
+      <c r="L3" s="58" t="n">
         <v>1</v>
       </c>
       <c r="M3" s="5" t="n"/>
-      <c r="N3" s="56" t="inlineStr">
+      <c r="N3" s="58" t="inlineStr">
         <is>
           <t>Servo</t>
         </is>
       </c>
-      <c r="O3" s="56" t="n">
+      <c r="O3" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="56" t="n">
+      <c r="P3" s="58" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q3" s="56" t="n">
+      <c r="Q3" s="58" t="n">
         <v>2.5</v>
       </c>
-      <c r="R3" s="56" t="n">
+      <c r="R3" s="58" t="n">
         <v>1</v>
       </c>
       <c r="S3" s="5" t="n"/>
-      <c r="T3" s="56" t="inlineStr">
+      <c r="T3" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U3" s="56" t="n">
+      <c r="U3" s="58" t="n">
         <v>0</v>
       </c>
       <c r="V3" s="5" t="n"/>
-      <c r="W3" s="56" t="inlineStr">
+      <c r="W3" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="X3" s="56" t="n">
+      <c r="X3" s="58" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="5" t="n"/>
-      <c r="Z3" s="56" t="n">
+      <c r="Z3" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="AA3" s="56" t="inlineStr">
+      <c r="AA3" s="58" t="inlineStr">
         <is>
           <t>1d6</t>
         </is>
       </c>
-      <c r="AB3" s="56" t="inlineStr">
+      <c r="AB3" s="58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="AC3" s="5" t="n"/>
-      <c r="AD3" s="56" t="inlineStr">
+      <c r="AD3" s="58" t="inlineStr">
         <is>
           <t>Físico</t>
         </is>
       </c>
-      <c r="AE3" s="56" t="inlineStr">
+      <c r="AE3" s="58" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
       </c>
       <c r="AF3" s="5" t="n"/>
-      <c r="AG3" s="56" t="n">
+      <c r="AG3" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="AH3" s="56" t="n">
+      <c r="AH3" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="AI3" s="56" t="n">
+      <c r="AI3" s="58" t="n">
         <v>1</v>
       </c>
       <c r="AJ3" s="5" t="n"/>
-      <c r="AK3" s="56">
+      <c r="AK3" s="58">
         <f>INVOCAÇÃO!$D$30</f>
         <v/>
       </c>
       <c r="AL3" s="5" t="n"/>
-      <c r="AM3" s="56" t="inlineStr">
+      <c r="AM3" s="58" t="inlineStr">
         <is>
           <t>nivel</t>
         </is>
       </c>
-      <c r="AN3" s="56" t="inlineStr">
+      <c r="AN3" s="58" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
       <c r="AO3" s="5" t="n"/>
-      <c r="AP3" s="56" t="n">
+      <c r="AP3" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="AQ3" s="56" t="n">
+      <c r="AQ3" s="58" t="n">
         <v>0</v>
       </c>
       <c r="AR3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="56" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>técnica</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>Coro</t>
         </is>
       </c>
-      <c r="C4" s="56" t="inlineStr">
+      <c r="C4" s="58" t="inlineStr">
         <is>
           <t>Constituição</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="58" t="inlineStr">
         <is>
           <t>Intelecto</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="58" t="inlineStr">
         <is>
           <t>Parrudo</t>
         </is>
       </c>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="56" t="inlineStr">
+      <c r="H4" s="58" t="inlineStr">
         <is>
           <t>Nado</t>
         </is>
       </c>
-      <c r="I4" s="56" t="inlineStr">
+      <c r="I4" s="58" t="inlineStr">
         <is>
           <t>Agarrar</t>
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="56" t="inlineStr">
+      <c r="K4" s="58" t="inlineStr">
         <is>
           <t>corpo amaldiçoado</t>
         </is>
       </c>
-      <c r="L4" s="56" t="n">
+      <c r="L4" s="58" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="5" t="n"/>
-      <c r="N4" s="56" t="inlineStr">
+      <c r="N4" s="58" t="inlineStr">
         <is>
           <t>Matilha</t>
         </is>
       </c>
-      <c r="O4" s="56" t="n">
+      <c r="O4" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="P4" s="56" t="n">
+      <c r="P4" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="56" t="n">
+      <c r="Q4" s="58" t="n">
         <v>2.5</v>
       </c>
-      <c r="R4" s="56" t="n">
+      <c r="R4" s="58" t="n">
         <v>1.5</v>
       </c>
       <c r="S4" s="5" t="n"/>
-      <c r="T4" s="56" t="inlineStr">
+      <c r="T4" s="58" t="inlineStr">
         <is>
           <t>Escalada</t>
         </is>
       </c>
-      <c r="U4" s="56" t="n">
+      <c r="U4" s="58" t="n">
         <v>2</v>
       </c>
       <c r="V4" s="5" t="n"/>
-      <c r="W4" s="56" t="inlineStr">
+      <c r="W4" s="58" t="inlineStr">
         <is>
           <t>Investir</t>
         </is>
       </c>
-      <c r="X4" s="56" t="n">
+      <c r="X4" s="58" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="5" t="n"/>
-      <c r="Z4" s="56" t="n">
+      <c r="Z4" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="AA4" s="56" t="inlineStr">
+      <c r="AA4" s="58" t="inlineStr">
         <is>
           <t>4d6</t>
         </is>
       </c>
-      <c r="AB4" s="56" t="inlineStr">
+      <c r="AB4" s="58" t="inlineStr">
         <is>
           <t>1d6</t>
         </is>
       </c>
       <c r="AC4" s="5" t="n"/>
-      <c r="AD4" s="56" t="inlineStr">
+      <c r="AD4" s="58" t="inlineStr">
         <is>
           <t>Vigor</t>
         </is>
       </c>
-      <c r="AE4" s="56" t="inlineStr">
+      <c r="AE4" s="58" t="inlineStr">
         <is>
           <t>Constituição</t>
         </is>
       </c>
       <c r="AF4" s="5" t="n"/>
-      <c r="AG4" s="56" t="n">
+      <c r="AG4" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="AH4" s="56" t="n">
+      <c r="AH4" s="58" t="n">
         <v>18</v>
       </c>
-      <c r="AI4" s="56" t="n">
+      <c r="AI4" s="58" t="n">
         <v>5</v>
       </c>
       <c r="AJ4" s="5" t="n"/>
-      <c r="AK4" s="56">
+      <c r="AK4" s="58">
         <f>INVOCAÇÃO!$L$30</f>
         <v/>
       </c>
       <c r="AL4" s="5" t="n"/>
-      <c r="AM4" s="56" t="inlineStr">
+      <c r="AM4" s="58" t="inlineStr">
         <is>
           <t>ess_dono</t>
         </is>
       </c>
-      <c r="AN4" s="56" t="inlineStr">
+      <c r="AN4" s="58" t="inlineStr">
         <is>
           <t>O7</t>
         </is>
       </c>
       <c r="AO4" s="5" t="n"/>
-      <c r="AP4" s="56" t="n">
+      <c r="AP4" s="58" t="n">
         <v>3</v>
       </c>
-      <c r="AQ4" s="56" t="n">
+      <c r="AQ4" s="58" t="n">
         <v>4</v>
       </c>
       <c r="AR4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t>maldição domada</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="56" t="inlineStr">
+      <c r="C5" s="58" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
       </c>
-      <c r="D5" s="56" t="inlineStr">
+      <c r="D5" s="58" t="inlineStr">
         <is>
           <t>Espírito</t>
         </is>
       </c>
-      <c r="E5" s="56" t="inlineStr">
+      <c r="E5" s="58" t="inlineStr">
         <is>
           <t>Voz</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
-      <c r="H5" s="56" t="inlineStr">
+      <c r="H5" s="58" t="inlineStr">
         <is>
           <t>Fala</t>
         </is>
       </c>
-      <c r="I5" s="56" t="inlineStr">
+      <c r="I5" s="58" t="inlineStr">
         <is>
           <t>Arrastar</t>
         </is>
       </c>
       <c r="J5" s="5" t="n"/>
-      <c r="K5" s="56" t="inlineStr">
+      <c r="K5" s="58" t="inlineStr">
         <is>
           <t>técnica</t>
         </is>
       </c>
-      <c r="L5" s="56" t="n">
+      <c r="L5" s="58" t="n">
         <v>2</v>
       </c>
       <c r="M5" s="5" t="n"/>
-      <c r="N5" s="56" t="inlineStr">
+      <c r="N5" s="58" t="inlineStr">
         <is>
           <t>Coro</t>
         </is>
       </c>
-      <c r="O5" s="56" t="n">
+      <c r="O5" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="56" t="n">
+      <c r="P5" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="56" t="n">
+      <c r="Q5" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="R5" s="56" t="n">
+      <c r="R5" s="58" t="n">
         <v>1</v>
       </c>
       <c r="S5" s="5" t="n"/>
-      <c r="T5" s="56" t="inlineStr">
+      <c r="T5" s="58" t="inlineStr">
         <is>
           <t>Nado</t>
         </is>
       </c>
-      <c r="U5" s="56" t="n">
+      <c r="U5" s="58" t="n">
         <v>2</v>
       </c>
       <c r="V5" s="5" t="n"/>
-      <c r="W5" s="56" t="inlineStr">
+      <c r="W5" s="58" t="inlineStr">
         <is>
           <t>Agarrar</t>
         </is>
       </c>
-      <c r="X5" s="56" t="n">
+      <c r="X5" s="58" t="n">
         <v>4</v>
       </c>
       <c r="Y5" s="5" t="n"/>
-      <c r="Z5" s="56" t="n">
+      <c r="Z5" s="58" t="n">
         <v>9</v>
       </c>
-      <c r="AA5" s="56" t="inlineStr">
+      <c r="AA5" s="58" t="inlineStr">
         <is>
           <t>6d6</t>
         </is>
       </c>
-      <c r="AB5" s="56" t="inlineStr">
+      <c r="AB5" s="58" t="inlineStr">
         <is>
           <t>2d6</t>
         </is>
       </c>
       <c r="AC5" s="5" t="n"/>
-      <c r="AD5" s="56" t="inlineStr">
+      <c r="AD5" s="58" t="inlineStr">
         <is>
           <t>Intelecto</t>
         </is>
       </c>
-      <c r="AE5" s="56" t="inlineStr">
+      <c r="AE5" s="58" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
       </c>
       <c r="AF5" s="5" t="n"/>
-      <c r="AG5" s="56" t="n">
+      <c r="AG5" s="58" t="n">
         <v>14</v>
       </c>
-      <c r="AH5" s="56" t="n">
+      <c r="AH5" s="58" t="n">
         <v>26</v>
       </c>
-      <c r="AI5" s="56" t="n">
+      <c r="AI5" s="58" t="n">
         <v>9</v>
       </c>
       <c r="AJ5" s="5" t="n"/>
-      <c r="AK5" s="56">
+      <c r="AK5" s="58">
         <f>INVOCAÇÃO!$T$30</f>
         <v/>
       </c>
       <c r="AL5" s="5" t="n"/>
-      <c r="AM5" s="56" t="inlineStr">
+      <c r="AM5" s="58" t="inlineStr">
         <is>
           <t>int_dono</t>
         </is>
       </c>
-      <c r="AN5" s="56" t="inlineStr">
+      <c r="AN5" s="58" t="inlineStr">
         <is>
           <t>Z7</t>
         </is>
       </c>
       <c r="AO5" s="5" t="n"/>
-      <c r="AP5" s="56" t="n">
+      <c r="AP5" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="AQ5" s="56" t="n">
+      <c r="AQ5" s="58" t="n">
         <v>8</v>
       </c>
       <c r="AR5" s="5" t="n"/>
@@ -7191,7 +7306,7 @@
     <row r="6">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="56" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -7200,23 +7315,23 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="56" t="inlineStr">
+      <c r="H6" s="58" t="inlineStr">
         <is>
           <t>Faro</t>
         </is>
       </c>
-      <c r="I6" s="56" t="inlineStr">
+      <c r="I6" s="58" t="inlineStr">
         <is>
           <t>Buscar</t>
         </is>
       </c>
       <c r="J6" s="5" t="n"/>
-      <c r="K6" s="56" t="inlineStr">
+      <c r="K6" s="58" t="inlineStr">
         <is>
           <t>maldição domada</t>
         </is>
       </c>
-      <c r="L6" s="56" t="n">
+      <c r="L6" s="58" t="n">
         <v>3</v>
       </c>
       <c r="M6" s="5" t="n"/>
@@ -7226,74 +7341,74 @@
       <c r="Q6" s="5" t="n"/>
       <c r="R6" s="5" t="n"/>
       <c r="S6" s="5" t="n"/>
-      <c r="T6" s="56" t="inlineStr">
+      <c r="T6" s="58" t="inlineStr">
         <is>
           <t>Fala</t>
         </is>
       </c>
-      <c r="U6" s="56" t="n">
+      <c r="U6" s="58" t="n">
         <v>3</v>
       </c>
       <c r="V6" s="5" t="n"/>
-      <c r="W6" s="56" t="inlineStr">
+      <c r="W6" s="58" t="inlineStr">
         <is>
           <t>Arrastar</t>
         </is>
       </c>
-      <c r="X6" s="56" t="n">
+      <c r="X6" s="58" t="n">
         <v>4</v>
       </c>
       <c r="Y6" s="5" t="n"/>
-      <c r="Z6" s="56" t="n">
+      <c r="Z6" s="58" t="n">
         <v>13</v>
       </c>
-      <c r="AA6" s="56" t="inlineStr">
+      <c r="AA6" s="58" t="inlineStr">
         <is>
           <t>8d6</t>
         </is>
       </c>
-      <c r="AB6" s="56" t="inlineStr">
+      <c r="AB6" s="58" t="inlineStr">
         <is>
           <t>3d6</t>
         </is>
       </c>
       <c r="AC6" s="5" t="n"/>
-      <c r="AD6" s="56" t="inlineStr">
+      <c r="AD6" s="58" t="inlineStr">
         <is>
           <t>Espírito</t>
         </is>
       </c>
-      <c r="AE6" s="56" t="inlineStr">
+      <c r="AE6" s="58" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
       </c>
       <c r="AF6" s="5" t="n"/>
-      <c r="AG6" s="56" t="n">
+      <c r="AG6" s="58" t="n">
         <v>18</v>
       </c>
       <c r="AH6" s="5" t="n"/>
-      <c r="AI6" s="56" t="n">
+      <c r="AI6" s="58" t="n">
         <v>13</v>
       </c>
       <c r="AJ6" s="5" t="n"/>
-      <c r="AK6" s="56">
+      <c r="AK6" s="58">
         <f>INVOCAÇÃO!$AB$30</f>
         <v/>
       </c>
       <c r="AL6" s="5" t="n"/>
-      <c r="AM6" s="56" t="inlineStr">
+      <c r="AM6" s="58" t="inlineStr">
         <is>
           <t>maestria</t>
         </is>
       </c>
-      <c r="AN6" s="56" t="inlineStr">
+      <c r="AN6" s="58" t="inlineStr">
         <is>
           <t>AK7</t>
         </is>
       </c>
       <c r="AO6" s="5" t="n"/>
-      <c r="AP6" s="56" t="n">
+      <c r="AP6" s="58" t="n">
         <v>7</v>
       </c>
       <c r="AQ6" s="5" t="n"/>
@@ -7307,12 +7422,12 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="56" t="inlineStr">
+      <c r="H7" s="58" t="inlineStr">
         <is>
           <t>Vigia</t>
         </is>
       </c>
-      <c r="I7" s="56" t="inlineStr">
+      <c r="I7" s="58" t="inlineStr">
         <is>
           <t>Cavar</t>
         </is>
@@ -7327,33 +7442,33 @@
       <c r="Q7" s="5" t="n"/>
       <c r="R7" s="5" t="n"/>
       <c r="S7" s="5" t="n"/>
-      <c r="T7" s="56" t="inlineStr">
+      <c r="T7" s="58" t="inlineStr">
         <is>
           <t>Faro</t>
         </is>
       </c>
-      <c r="U7" s="56" t="n">
+      <c r="U7" s="58" t="n">
         <v>5</v>
       </c>
       <c r="V7" s="5" t="n"/>
-      <c r="W7" s="56" t="inlineStr">
+      <c r="W7" s="58" t="inlineStr">
         <is>
           <t>Buscar</t>
         </is>
       </c>
-      <c r="X7" s="56" t="n">
+      <c r="X7" s="58" t="n">
         <v>4</v>
       </c>
       <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="56" t="n">
+      <c r="Z7" s="58" t="n">
         <v>17</v>
       </c>
-      <c r="AA7" s="56" t="inlineStr">
+      <c r="AA7" s="58" t="inlineStr">
         <is>
           <t>10d6</t>
         </is>
       </c>
-      <c r="AB7" s="56" t="inlineStr">
+      <c r="AB7" s="58" t="inlineStr">
         <is>
           <t>4d6</t>
         </is>
@@ -7362,31 +7477,31 @@
       <c r="AD7" s="5" t="n"/>
       <c r="AE7" s="5" t="n"/>
       <c r="AF7" s="5" t="n"/>
-      <c r="AG7" s="56" t="n">
+      <c r="AG7" s="58" t="n">
         <v>22</v>
       </c>
       <c r="AH7" s="5" t="n"/>
-      <c r="AI7" s="56" t="n">
+      <c r="AI7" s="58" t="n">
         <v>17</v>
       </c>
       <c r="AJ7" s="5" t="n"/>
-      <c r="AK7" s="56">
+      <c r="AK7" s="58">
         <f>INVOCAÇÃO!$AJ$30</f>
         <v/>
       </c>
       <c r="AL7" s="5" t="n"/>
-      <c r="AM7" s="56" t="inlineStr">
+      <c r="AM7" s="58" t="inlineStr">
         <is>
           <t>marcos</t>
         </is>
       </c>
-      <c r="AN7" s="56" t="inlineStr">
+      <c r="AN7" s="58" t="inlineStr">
         <is>
           <t>D11</t>
         </is>
       </c>
       <c r="AO7" s="5" t="n"/>
-      <c r="AP7" s="56" t="n">
+      <c r="AP7" s="58" t="n">
         <v>8</v>
       </c>
       <c r="AQ7" s="5" t="n"/>
@@ -7400,12 +7515,12 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="56" t="inlineStr">
+      <c r="H8" s="58" t="inlineStr">
         <is>
           <t>Miúdo</t>
         </is>
       </c>
-      <c r="I8" s="56" t="inlineStr">
+      <c r="I8" s="58" t="inlineStr">
         <is>
           <t>Interpor</t>
         </is>
@@ -7420,33 +7535,33 @@
       <c r="Q8" s="5" t="n"/>
       <c r="R8" s="5" t="n"/>
       <c r="S8" s="5" t="n"/>
-      <c r="T8" s="56" t="inlineStr">
+      <c r="T8" s="58" t="inlineStr">
         <is>
           <t>Vigia</t>
         </is>
       </c>
-      <c r="U8" s="56" t="n">
+      <c r="U8" s="58" t="n">
         <v>5</v>
       </c>
       <c r="V8" s="5" t="n"/>
-      <c r="W8" s="56" t="inlineStr">
+      <c r="W8" s="58" t="inlineStr">
         <is>
           <t>Cavar</t>
         </is>
       </c>
-      <c r="X8" s="56" t="n">
+      <c r="X8" s="58" t="n">
         <v>4</v>
       </c>
       <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="56" t="n">
+      <c r="Z8" s="58" t="n">
         <v>21</v>
       </c>
-      <c r="AA8" s="56" t="inlineStr">
+      <c r="AA8" s="58" t="inlineStr">
         <is>
           <t>13d6</t>
         </is>
       </c>
-      <c r="AB8" s="56" t="inlineStr">
+      <c r="AB8" s="58" t="inlineStr">
         <is>
           <t>5d6</t>
         </is>
@@ -7455,22 +7570,22 @@
       <c r="AD8" s="5" t="n"/>
       <c r="AE8" s="5" t="n"/>
       <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="56" t="n">
+      <c r="AG8" s="58" t="n">
         <v>26</v>
       </c>
       <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="56" t="n">
+      <c r="AI8" s="58" t="n">
         <v>21</v>
       </c>
       <c r="AJ8" s="5" t="n"/>
       <c r="AK8" s="5" t="n"/>
       <c r="AL8" s="5" t="n"/>
-      <c r="AM8" s="56" t="inlineStr">
+      <c r="AM8" s="58" t="inlineStr">
         <is>
           <t>classe</t>
         </is>
       </c>
-      <c r="AN8" s="56" t="inlineStr">
+      <c r="AN8" s="58" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
@@ -7488,12 +7603,12 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="56" t="inlineStr">
+      <c r="H9" s="58" t="inlineStr">
         <is>
           <t>Voo</t>
         </is>
       </c>
-      <c r="I9" s="56" t="inlineStr">
+      <c r="I9" s="58" t="inlineStr">
         <is>
           <t>Chamariz</t>
         </is>
@@ -7508,33 +7623,33 @@
       <c r="Q9" s="5" t="n"/>
       <c r="R9" s="5" t="n"/>
       <c r="S9" s="5" t="n"/>
-      <c r="T9" s="56" t="inlineStr">
+      <c r="T9" s="58" t="inlineStr">
         <is>
           <t>Miúdo</t>
         </is>
       </c>
-      <c r="U9" s="56" t="n">
+      <c r="U9" s="58" t="n">
         <v>7</v>
       </c>
       <c r="V9" s="5" t="n"/>
-      <c r="W9" s="56" t="inlineStr">
+      <c r="W9" s="58" t="inlineStr">
         <is>
           <t>Interpor</t>
         </is>
       </c>
-      <c r="X9" s="56" t="n">
+      <c r="X9" s="58" t="n">
         <v>8</v>
       </c>
       <c r="Y9" s="5" t="n"/>
-      <c r="Z9" s="56" t="n">
+      <c r="Z9" s="58" t="n">
         <v>26</v>
       </c>
-      <c r="AA9" s="56" t="inlineStr">
+      <c r="AA9" s="58" t="inlineStr">
         <is>
           <t>15d6</t>
         </is>
       </c>
-      <c r="AB9" s="56" t="inlineStr">
+      <c r="AB9" s="58" t="inlineStr">
         <is>
           <t>6d6</t>
         </is>
@@ -7543,22 +7658,22 @@
       <c r="AD9" s="5" t="n"/>
       <c r="AE9" s="5" t="n"/>
       <c r="AF9" s="5" t="n"/>
-      <c r="AG9" s="56" t="n">
+      <c r="AG9" s="58" t="n">
         <v>30</v>
       </c>
       <c r="AH9" s="5" t="n"/>
-      <c r="AI9" s="56" t="n">
+      <c r="AI9" s="58" t="n">
         <v>26</v>
       </c>
       <c r="AJ9" s="5" t="n"/>
       <c r="AK9" s="5" t="n"/>
       <c r="AL9" s="5" t="n"/>
-      <c r="AM9" s="56" t="inlineStr">
+      <c r="AM9" s="58" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
       </c>
-      <c r="AN9" s="56" t="inlineStr">
+      <c r="AN9" s="58" t="inlineStr">
         <is>
           <t>D19</t>
         </is>
@@ -7576,7 +7691,7 @@
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="56" t="inlineStr">
+      <c r="H10" s="58" t="inlineStr">
         <is>
           <t>Montaria</t>
         </is>
@@ -7592,21 +7707,21 @@
       <c r="Q10" s="5" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="S10" s="5" t="n"/>
-      <c r="T10" s="56" t="inlineStr">
+      <c r="T10" s="58" t="inlineStr">
         <is>
           <t>Voo</t>
         </is>
       </c>
-      <c r="U10" s="56" t="n">
+      <c r="U10" s="58" t="n">
         <v>8</v>
       </c>
       <c r="V10" s="5" t="n"/>
-      <c r="W10" s="56" t="inlineStr">
+      <c r="W10" s="58" t="inlineStr">
         <is>
           <t>Chamariz</t>
         </is>
       </c>
-      <c r="X10" s="56" t="n">
+      <c r="X10" s="58" t="n">
         <v>8</v>
       </c>
       <c r="Y10" s="5" t="n"/>
@@ -7623,12 +7738,12 @@
       <c r="AJ10" s="5" t="n"/>
       <c r="AK10" s="5" t="n"/>
       <c r="AL10" s="5" t="n"/>
-      <c r="AM10" s="56" t="inlineStr">
+      <c r="AM10" s="58" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="AN10" s="56" t="inlineStr">
+      <c r="AN10" s="58" t="inlineStr">
         <is>
           <t>Z19</t>
         </is>
@@ -7646,7 +7761,7 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="56" t="inlineStr">
+      <c r="H11" s="58" t="inlineStr">
         <is>
           <t>Fisgada</t>
         </is>
@@ -7662,12 +7777,12 @@
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
-      <c r="T11" s="56" t="inlineStr">
+      <c r="T11" s="58" t="inlineStr">
         <is>
           <t>Montaria</t>
         </is>
       </c>
-      <c r="U11" s="56" t="n">
+      <c r="U11" s="58" t="n">
         <v>8</v>
       </c>
       <c r="V11" s="5" t="n"/>
@@ -7687,12 +7802,12 @@
       <c r="AJ11" s="5" t="n"/>
       <c r="AK11" s="5" t="n"/>
       <c r="AL11" s="5" t="n"/>
-      <c r="AM11" s="56" t="inlineStr">
+      <c r="AM11" s="58" t="inlineStr">
         <is>
           <t>trilha</t>
         </is>
       </c>
-      <c r="AN11" s="56" t="inlineStr">
+      <c r="AN11" s="58" t="inlineStr">
         <is>
           <t>AK19</t>
         </is>
@@ -7710,7 +7825,7 @@
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="56" t="inlineStr">
+      <c r="H12" s="58" t="inlineStr">
         <is>
           <t>Emboscada</t>
         </is>
@@ -7726,12 +7841,12 @@
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
-      <c r="T12" s="56" t="inlineStr">
+      <c r="T12" s="58" t="inlineStr">
         <is>
           <t>Fisgada</t>
         </is>
       </c>
-      <c r="U12" s="56" t="n">
+      <c r="U12" s="58" t="n">
         <v>8</v>
       </c>
       <c r="V12" s="5" t="n"/>
@@ -7751,12 +7866,12 @@
       <c r="AJ12" s="5" t="n"/>
       <c r="AK12" s="5" t="n"/>
       <c r="AL12" s="5" t="n"/>
-      <c r="AM12" s="56" t="inlineStr">
+      <c r="AM12" s="58" t="inlineStr">
         <is>
           <t>sintonia</t>
         </is>
       </c>
-      <c r="AN12" s="56" t="inlineStr">
+      <c r="AN12" s="58" t="inlineStr">
         <is>
           <t>D22</t>
         </is>
@@ -7774,7 +7889,7 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="56" t="inlineStr">
+      <c r="H13" s="58" t="inlineStr">
         <is>
           <t>Jorro</t>
         </is>
@@ -7790,12 +7905,12 @@
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
-      <c r="T13" s="56" t="inlineStr">
+      <c r="T13" s="58" t="inlineStr">
         <is>
           <t>Emboscada</t>
         </is>
       </c>
-      <c r="U13" s="56" t="n">
+      <c r="U13" s="58" t="n">
         <v>8</v>
       </c>
       <c r="V13" s="5" t="n"/>
@@ -7815,12 +7930,12 @@
       <c r="AJ13" s="5" t="n"/>
       <c r="AK13" s="5" t="n"/>
       <c r="AL13" s="5" t="n"/>
-      <c r="AM13" s="56" t="inlineStr">
+      <c r="AM13" s="58" t="inlineStr">
         <is>
           <t>pontos_atributo</t>
         </is>
       </c>
-      <c r="AN13" s="56" t="inlineStr">
+      <c r="AN13" s="58" t="inlineStr">
         <is>
           <t>D35</t>
         </is>
@@ -7838,7 +7953,7 @@
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
-      <c r="H14" s="56" t="inlineStr">
+      <c r="H14" s="58" t="inlineStr">
         <is>
           <t>Graúdo</t>
         </is>
@@ -7854,12 +7969,12 @@
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
-      <c r="T14" s="56" t="inlineStr">
+      <c r="T14" s="58" t="inlineStr">
         <is>
           <t>Jorro</t>
         </is>
       </c>
-      <c r="U14" s="56" t="n">
+      <c r="U14" s="58" t="n">
         <v>8</v>
       </c>
       <c r="V14" s="5" t="n"/>
@@ -7879,12 +7994,12 @@
       <c r="AJ14" s="5" t="n"/>
       <c r="AK14" s="5" t="n"/>
       <c r="AL14" s="5" t="n"/>
-      <c r="AM14" s="56" t="inlineStr">
+      <c r="AM14" s="58" t="inlineStr">
         <is>
           <t>pontos_disp</t>
         </is>
       </c>
-      <c r="AN14" s="56" t="inlineStr">
+      <c r="AN14" s="58" t="inlineStr">
         <is>
           <t>O35</t>
         </is>
@@ -7902,7 +8017,7 @@
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
-      <c r="H15" s="56" t="inlineStr">
+      <c r="H15" s="58" t="inlineStr">
         <is>
           <t>Remoto</t>
         </is>
@@ -7918,12 +8033,12 @@
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
-      <c r="T15" s="56" t="inlineStr">
+      <c r="T15" s="58" t="inlineStr">
         <is>
           <t>Graúdo</t>
         </is>
       </c>
-      <c r="U15" s="56" t="n">
+      <c r="U15" s="58" t="n">
         <v>8</v>
       </c>
       <c r="V15" s="5" t="n"/>
@@ -7943,12 +8058,12 @@
       <c r="AJ15" s="5" t="n"/>
       <c r="AK15" s="5" t="n"/>
       <c r="AL15" s="5" t="n"/>
-      <c r="AM15" s="56" t="inlineStr">
+      <c r="AM15" s="58" t="inlineStr">
         <is>
           <t>aviso_atributo</t>
         </is>
       </c>
-      <c r="AN15" s="56" t="inlineStr">
+      <c r="AN15" s="58" t="inlineStr">
         <is>
           <t>Z35</t>
         </is>
@@ -7978,12 +8093,12 @@
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
-      <c r="T16" s="56" t="inlineStr">
+      <c r="T16" s="58" t="inlineStr">
         <is>
           <t>Remoto</t>
         </is>
       </c>
-      <c r="U16" s="56" t="n">
+      <c r="U16" s="58" t="n">
         <v>8</v>
       </c>
       <c r="V16" s="5" t="n"/>
@@ -8003,12 +8118,12 @@
       <c r="AJ16" s="5" t="n"/>
       <c r="AK16" s="5" t="n"/>
       <c r="AL16" s="5" t="n"/>
-      <c r="AM16" s="56" t="inlineStr">
+      <c r="AM16" s="58" t="inlineStr">
         <is>
           <t>atr_acerto</t>
         </is>
       </c>
-      <c r="AN16" s="56" t="inlineStr">
+      <c r="AN16" s="58" t="inlineStr">
         <is>
           <t>D43</t>
         </is>
@@ -8057,12 +8172,12 @@
       <c r="AJ17" s="5" t="n"/>
       <c r="AK17" s="5" t="n"/>
       <c r="AL17" s="5" t="n"/>
-      <c r="AM17" s="56" t="inlineStr">
+      <c r="AM17" s="58" t="inlineStr">
         <is>
           <t>acerto</t>
         </is>
       </c>
-      <c r="AN17" s="56" t="inlineStr">
+      <c r="AN17" s="58" t="inlineStr">
         <is>
           <t>O43</t>
         </is>
@@ -8111,12 +8226,12 @@
       <c r="AJ18" s="5" t="n"/>
       <c r="AK18" s="5" t="n"/>
       <c r="AL18" s="5" t="n"/>
-      <c r="AM18" s="56" t="inlineStr">
+      <c r="AM18" s="58" t="inlineStr">
         <is>
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="AN18" s="56" t="inlineStr">
+      <c r="AN18" s="58" t="inlineStr">
         <is>
           <t>Z43</t>
         </is>
@@ -8165,12 +8280,12 @@
       <c r="AJ19" s="5" t="n"/>
       <c r="AK19" s="5" t="n"/>
       <c r="AL19" s="5" t="n"/>
-      <c r="AM19" s="56" t="inlineStr">
+      <c r="AM19" s="58" t="inlineStr">
         <is>
           <t>defesa</t>
         </is>
       </c>
-      <c r="AN19" s="56" t="inlineStr">
+      <c r="AN19" s="58" t="inlineStr">
         <is>
           <t>AK43</t>
         </is>
@@ -8219,12 +8334,12 @@
       <c r="AJ20" s="5" t="n"/>
       <c r="AK20" s="5" t="n"/>
       <c r="AL20" s="5" t="n"/>
-      <c r="AM20" s="56" t="inlineStr">
+      <c r="AM20" s="58" t="inlineStr">
         <is>
           <t>critico</t>
         </is>
       </c>
-      <c r="AN20" s="56" t="inlineStr">
+      <c r="AN20" s="58" t="inlineStr">
         <is>
           <t>D46</t>
         </is>
@@ -8273,12 +8388,12 @@
       <c r="AJ21" s="5" t="n"/>
       <c r="AK21" s="5" t="n"/>
       <c r="AL21" s="5" t="n"/>
-      <c r="AM21" s="56" t="inlineStr">
+      <c r="AM21" s="58" t="inlineStr">
         <is>
           <t>tr_treinado</t>
         </is>
       </c>
-      <c r="AN21" s="56" t="inlineStr">
+      <c r="AN21" s="58" t="inlineStr">
         <is>
           <t>O46</t>
         </is>
@@ -8327,12 +8442,12 @@
       <c r="AJ22" s="5" t="n"/>
       <c r="AK22" s="5" t="n"/>
       <c r="AL22" s="5" t="n"/>
-      <c r="AM22" s="56" t="inlineStr">
+      <c r="AM22" s="58" t="inlineStr">
         <is>
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="AN22" s="56" t="inlineStr">
+      <c r="AN22" s="58" t="inlineStr">
         <is>
           <t>Z46</t>
         </is>
@@ -8381,12 +8496,12 @@
       <c r="AJ23" s="5" t="n"/>
       <c r="AK23" s="5" t="n"/>
       <c r="AL23" s="5" t="n"/>
-      <c r="AM23" s="56" t="inlineStr">
+      <c r="AM23" s="58" t="inlineStr">
         <is>
           <t>tr_Físico</t>
         </is>
       </c>
-      <c r="AN23" s="56" t="inlineStr">
+      <c r="AN23" s="58" t="inlineStr">
         <is>
           <t>Q50</t>
         </is>
@@ -8435,12 +8550,12 @@
       <c r="AJ24" s="5" t="n"/>
       <c r="AK24" s="5" t="n"/>
       <c r="AL24" s="5" t="n"/>
-      <c r="AM24" s="56" t="inlineStr">
+      <c r="AM24" s="58" t="inlineStr">
         <is>
           <t>tr_extra_Físico</t>
         </is>
       </c>
-      <c r="AN24" s="56" t="inlineStr">
+      <c r="AN24" s="58" t="inlineStr">
         <is>
           <t>K50</t>
         </is>
@@ -8489,12 +8604,12 @@
       <c r="AJ25" s="5" t="n"/>
       <c r="AK25" s="5" t="n"/>
       <c r="AL25" s="5" t="n"/>
-      <c r="AM25" s="56" t="inlineStr">
+      <c r="AM25" s="58" t="inlineStr">
         <is>
           <t>tr_Vigor</t>
         </is>
       </c>
-      <c r="AN25" s="56" t="inlineStr">
+      <c r="AN25" s="58" t="inlineStr">
         <is>
           <t>AM50</t>
         </is>
@@ -8543,12 +8658,12 @@
       <c r="AJ26" s="5" t="n"/>
       <c r="AK26" s="5" t="n"/>
       <c r="AL26" s="5" t="n"/>
-      <c r="AM26" s="56" t="inlineStr">
+      <c r="AM26" s="58" t="inlineStr">
         <is>
           <t>tr_extra_Vigor</t>
         </is>
       </c>
-      <c r="AN26" s="56" t="inlineStr">
+      <c r="AN26" s="58" t="inlineStr">
         <is>
           <t>AG50</t>
         </is>
@@ -8597,12 +8712,12 @@
       <c r="AJ27" s="5" t="n"/>
       <c r="AK27" s="5" t="n"/>
       <c r="AL27" s="5" t="n"/>
-      <c r="AM27" s="56" t="inlineStr">
+      <c r="AM27" s="58" t="inlineStr">
         <is>
           <t>tr_Intelecto</t>
         </is>
       </c>
-      <c r="AN27" s="56" t="inlineStr">
+      <c r="AN27" s="58" t="inlineStr">
         <is>
           <t>Q51</t>
         </is>
@@ -8651,12 +8766,12 @@
       <c r="AJ28" s="5" t="n"/>
       <c r="AK28" s="5" t="n"/>
       <c r="AL28" s="5" t="n"/>
-      <c r="AM28" s="56" t="inlineStr">
+      <c r="AM28" s="58" t="inlineStr">
         <is>
           <t>tr_extra_Intelecto</t>
         </is>
       </c>
-      <c r="AN28" s="56" t="inlineStr">
+      <c r="AN28" s="58" t="inlineStr">
         <is>
           <t>K51</t>
         </is>
@@ -8705,12 +8820,12 @@
       <c r="AJ29" s="5" t="n"/>
       <c r="AK29" s="5" t="n"/>
       <c r="AL29" s="5" t="n"/>
-      <c r="AM29" s="56" t="inlineStr">
+      <c r="AM29" s="58" t="inlineStr">
         <is>
           <t>tr_Espírito</t>
         </is>
       </c>
-      <c r="AN29" s="56" t="inlineStr">
+      <c r="AN29" s="58" t="inlineStr">
         <is>
           <t>AM51</t>
         </is>
@@ -8759,12 +8874,12 @@
       <c r="AJ30" s="5" t="n"/>
       <c r="AK30" s="5" t="n"/>
       <c r="AL30" s="5" t="n"/>
-      <c r="AM30" s="56" t="inlineStr">
+      <c r="AM30" s="58" t="inlineStr">
         <is>
           <t>tr_extra_Espírito</t>
         </is>
       </c>
-      <c r="AN30" s="56" t="inlineStr">
+      <c r="AN30" s="58" t="inlineStr">
         <is>
           <t>AG51</t>
         </is>
@@ -8775,744 +8890,792 @@
       <c r="AR30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="AM31" s="57" t="inlineStr">
+      <c r="AM31" s="59" t="inlineStr">
         <is>
           <t>vida_max</t>
         </is>
       </c>
-      <c r="AN31" s="57" t="inlineStr">
+      <c r="AN31" s="59" t="inlineStr">
         <is>
           <t>D59</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="AM32" s="57" t="inlineStr">
+      <c r="AM32" s="59" t="inlineStr">
         <is>
           <t>vida</t>
         </is>
       </c>
-      <c r="AN32" s="57" t="inlineStr">
+      <c r="AN32" s="59" t="inlineStr">
         <is>
           <t>O59</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="AM33" s="57" t="inlineStr">
+      <c r="AM33" s="59" t="inlineStr">
         <is>
           <t>corpos</t>
         </is>
       </c>
-      <c r="AN33" s="57" t="inlineStr">
+      <c r="AN33" s="59" t="inlineStr">
         <is>
           <t>Z59</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="AM34" s="57" t="inlineStr">
+      <c r="AM34" s="59" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="AN34" s="57" t="inlineStr">
+      <c r="AN34" s="59" t="inlineStr">
         <is>
           <t>AK59</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="AM35" s="57" t="inlineStr">
+      <c r="AM35" s="59" t="inlineStr">
         <is>
           <t>regua</t>
         </is>
       </c>
-      <c r="AN35" s="57" t="inlineStr">
+      <c r="AN35" s="59" t="inlineStr">
         <is>
           <t>D65</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="AM36" s="57" t="inlineStr">
+      <c r="AM36" s="59" t="inlineStr">
         <is>
           <t>meia_regua</t>
         </is>
       </c>
-      <c r="AN36" s="57" t="inlineStr">
+      <c r="AN36" s="59" t="inlineStr">
         <is>
           <t>O65</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="AM37" s="57" t="inlineStr">
+      <c r="AM37" s="59" t="inlineStr">
         <is>
           <t>volta_com</t>
         </is>
       </c>
-      <c r="AN37" s="57" t="inlineStr">
+      <c r="AN37" s="59" t="inlineStr">
         <is>
           <t>Z65</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="AM38" s="57" t="inlineStr">
+      <c r="AM38" s="59" t="inlineStr">
         <is>
           <t>orcamento</t>
         </is>
       </c>
-      <c r="AN38" s="57" t="inlineStr">
+      <c r="AN38" s="59" t="inlineStr">
         <is>
           <t>D76</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="AM39" s="57" t="inlineStr">
+      <c r="AM39" s="59" t="inlineStr">
         <is>
           <t>gasto</t>
         </is>
       </c>
-      <c r="AN39" s="57" t="inlineStr">
+      <c r="AN39" s="59" t="inlineStr">
         <is>
           <t>D92</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="AM40" s="57" t="inlineStr">
+      <c r="AM40" s="59" t="inlineStr">
         <is>
           <t>sobra</t>
         </is>
       </c>
-      <c r="AN40" s="57" t="inlineStr">
+      <c r="AN40" s="59" t="inlineStr">
         <is>
           <t>O92</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="AM41" s="57" t="inlineStr">
+      <c r="AM41" s="59" t="inlineStr">
         <is>
           <t>investir</t>
         </is>
       </c>
-      <c r="AN41" s="57" t="inlineStr">
+      <c r="AN41" s="59" t="inlineStr">
         <is>
           <t>D100</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="AM42" s="57" t="inlineStr">
-        <is>
-          <t>cd_pendente</t>
-        </is>
-      </c>
-      <c r="AN42" s="57" t="inlineStr">
+      <c r="AM42" s="59" t="inlineStr">
+        <is>
+          <t>cd_atributo</t>
+        </is>
+      </c>
+      <c r="AN42" s="59" t="inlineStr">
         <is>
           <t>D117</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="AM43" s="57" t="inlineStr">
+      <c r="AM43" s="59" t="inlineStr">
+        <is>
+          <t>cd_preito</t>
+        </is>
+      </c>
+      <c r="AN43" s="59" t="inlineStr">
+        <is>
+          <t>O117</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="AM44" s="59" t="inlineStr">
+        <is>
+          <t>cd_bonus</t>
+        </is>
+      </c>
+      <c r="AN44" s="59" t="inlineStr">
+        <is>
+          <t>Z117</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="AM45" s="59" t="inlineStr">
+        <is>
+          <t>cd</t>
+        </is>
+      </c>
+      <c r="AN45" s="59" t="inlineStr">
+        <is>
+          <t>AK117</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="AM46" s="59" t="inlineStr">
+        <is>
+          <t>cd_confere</t>
+        </is>
+      </c>
+      <c r="AN46" s="59" t="inlineStr">
+        <is>
+          <t>D121</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="AM47" s="59" t="inlineStr">
         <is>
           <t>atr_Força</t>
         </is>
       </c>
-      <c r="AN43" s="57" t="inlineStr">
+      <c r="AN47" s="59" t="inlineStr">
         <is>
           <t>D30</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="AM44" s="57" t="inlineStr">
+    <row r="48">
+      <c r="AM48" s="59" t="inlineStr">
         <is>
           <t>atr_Destreza</t>
         </is>
       </c>
-      <c r="AN44" s="57" t="inlineStr">
+      <c r="AN48" s="59" t="inlineStr">
         <is>
           <t>L30</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="AM45" s="57" t="inlineStr">
+    <row r="49">
+      <c r="AM49" s="59" t="inlineStr">
         <is>
           <t>atr_Constituição</t>
         </is>
       </c>
-      <c r="AN45" s="57" t="inlineStr">
+      <c r="AN49" s="59" t="inlineStr">
         <is>
           <t>T30</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="AM46" s="57" t="inlineStr">
+    <row r="50">
+      <c r="AM50" s="59" t="inlineStr">
         <is>
           <t>atr_Inteligência</t>
         </is>
       </c>
-      <c r="AN46" s="57" t="inlineStr">
+      <c r="AN50" s="59" t="inlineStr">
         <is>
           <t>AB30</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="AM47" s="57" t="inlineStr">
+    <row r="51">
+      <c r="AM51" s="59" t="inlineStr">
         <is>
           <t>atr_Essência</t>
         </is>
       </c>
-      <c r="AN47" s="57" t="inlineStr">
+      <c r="AN51" s="59" t="inlineStr">
         <is>
           <t>AJ30</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="AM48" s="57" t="inlineStr">
+    <row r="52">
+      <c r="AM52" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_1</t>
         </is>
       </c>
-      <c r="AN48" s="57" t="inlineStr">
+      <c r="AN52" s="59" t="inlineStr">
         <is>
           <t>S80</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="AM49" s="57" t="inlineStr">
+    <row r="53">
+      <c r="AM53" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_2</t>
         </is>
       </c>
-      <c r="AN49" s="57" t="inlineStr">
+      <c r="AN53" s="59" t="inlineStr">
         <is>
           <t>S81</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="AM50" s="57" t="inlineStr">
+    <row r="54">
+      <c r="AM54" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_3</t>
         </is>
       </c>
-      <c r="AN50" s="57" t="inlineStr">
+      <c r="AN54" s="59" t="inlineStr">
         <is>
           <t>S82</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="AM51" s="57" t="inlineStr">
+    <row r="55">
+      <c r="AM55" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_4</t>
         </is>
       </c>
-      <c r="AN51" s="57" t="inlineStr">
+      <c r="AN55" s="59" t="inlineStr">
         <is>
           <t>S83</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="AM52" s="57" t="inlineStr">
+    <row r="56">
+      <c r="AM56" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_5</t>
         </is>
       </c>
-      <c r="AN52" s="57" t="inlineStr">
+      <c r="AN56" s="59" t="inlineStr">
         <is>
           <t>S84</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="AM53" s="57" t="inlineStr">
+    <row r="57">
+      <c r="AM57" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_6</t>
         </is>
       </c>
-      <c r="AN53" s="57" t="inlineStr">
+      <c r="AN57" s="59" t="inlineStr">
         <is>
           <t>S85</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="AM54" s="57" t="inlineStr">
+    <row r="58">
+      <c r="AM58" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_7</t>
         </is>
       </c>
-      <c r="AN54" s="57" t="inlineStr">
+      <c r="AN58" s="59" t="inlineStr">
         <is>
           <t>S86</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="AM55" s="57" t="inlineStr">
+    <row r="59">
+      <c r="AM59" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_8</t>
         </is>
       </c>
-      <c r="AN55" s="57" t="inlineStr">
+      <c r="AN59" s="59" t="inlineStr">
         <is>
           <t>S87</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="AM56" s="57" t="inlineStr">
+    <row r="60">
+      <c r="AM60" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_9</t>
         </is>
       </c>
-      <c r="AN56" s="57" t="inlineStr">
+      <c r="AN60" s="59" t="inlineStr">
         <is>
           <t>S88</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="AM57" s="57" t="inlineStr">
+    <row r="61">
+      <c r="AM61" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_10</t>
         </is>
       </c>
-      <c r="AN57" s="57" t="inlineStr">
+      <c r="AN61" s="59" t="inlineStr">
         <is>
           <t>AO80</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="AM58" s="57" t="inlineStr">
+    <row r="62">
+      <c r="AM62" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_11</t>
         </is>
       </c>
-      <c r="AN58" s="57" t="inlineStr">
+      <c r="AN62" s="59" t="inlineStr">
         <is>
           <t>AO81</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="AM59" s="57" t="inlineStr">
+    <row r="63">
+      <c r="AM63" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_12</t>
         </is>
       </c>
-      <c r="AN59" s="57" t="inlineStr">
+      <c r="AN63" s="59" t="inlineStr">
         <is>
           <t>AO82</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="AM60" s="57" t="inlineStr">
+    <row r="64">
+      <c r="AM64" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_13</t>
         </is>
       </c>
-      <c r="AN60" s="57" t="inlineStr">
+      <c r="AN64" s="59" t="inlineStr">
         <is>
           <t>AO83</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="AM61" s="57" t="inlineStr">
+    <row r="65">
+      <c r="AM65" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_14</t>
         </is>
       </c>
-      <c r="AN61" s="57" t="inlineStr">
+      <c r="AN65" s="59" t="inlineStr">
         <is>
           <t>AO84</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="AM62" s="57" t="inlineStr">
+    <row r="66">
+      <c r="AM66" s="59" t="inlineStr">
         <is>
           <t>slot_pontos_15</t>
         </is>
       </c>
-      <c r="AN62" s="57" t="inlineStr">
+      <c r="AN66" s="59" t="inlineStr">
         <is>
           <t>AO85</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="AM63" s="57" t="inlineStr">
+    <row r="67">
+      <c r="AM67" s="59" t="inlineStr">
         <is>
           <t>traco_1</t>
         </is>
       </c>
-      <c r="AN63" s="57" t="inlineStr">
+      <c r="AN67" s="59" t="inlineStr">
         <is>
           <t>D80</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="AM64" s="57" t="inlineStr">
+    <row r="68">
+      <c r="AM68" s="59" t="inlineStr">
         <is>
           <t>traco_2</t>
         </is>
       </c>
-      <c r="AN64" s="57" t="inlineStr">
+      <c r="AN68" s="59" t="inlineStr">
         <is>
           <t>D81</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="AM65" s="57" t="inlineStr">
+    <row r="69">
+      <c r="AM69" s="59" t="inlineStr">
         <is>
           <t>traco_3</t>
         </is>
       </c>
-      <c r="AN65" s="57" t="inlineStr">
+      <c r="AN69" s="59" t="inlineStr">
         <is>
           <t>D82</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="AM66" s="57" t="inlineStr">
+    <row r="70">
+      <c r="AM70" s="59" t="inlineStr">
         <is>
           <t>traco_4</t>
         </is>
       </c>
-      <c r="AN66" s="57" t="inlineStr">
+      <c r="AN70" s="59" t="inlineStr">
         <is>
           <t>D83</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="AM67" s="57" t="inlineStr">
+    <row r="71">
+      <c r="AM71" s="59" t="inlineStr">
         <is>
           <t>traco_5</t>
         </is>
       </c>
-      <c r="AN67" s="57" t="inlineStr">
+      <c r="AN71" s="59" t="inlineStr">
         <is>
           <t>D84</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="AM68" s="57" t="inlineStr">
+    <row r="72">
+      <c r="AM72" s="59" t="inlineStr">
         <is>
           <t>traco_6</t>
         </is>
       </c>
-      <c r="AN68" s="57" t="inlineStr">
+      <c r="AN72" s="59" t="inlineStr">
         <is>
           <t>D85</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="AM69" s="57" t="inlineStr">
+    <row r="73">
+      <c r="AM73" s="59" t="inlineStr">
         <is>
           <t>traco_7</t>
         </is>
       </c>
-      <c r="AN69" s="57" t="inlineStr">
+      <c r="AN73" s="59" t="inlineStr">
         <is>
           <t>D86</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="AM70" s="57" t="inlineStr">
+    <row r="74">
+      <c r="AM74" s="59" t="inlineStr">
         <is>
           <t>traco_8</t>
         </is>
       </c>
-      <c r="AN70" s="57" t="inlineStr">
+      <c r="AN74" s="59" t="inlineStr">
         <is>
           <t>D87</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="AM71" s="57" t="inlineStr">
+    <row r="75">
+      <c r="AM75" s="59" t="inlineStr">
         <is>
           <t>traco_9</t>
         </is>
       </c>
-      <c r="AN71" s="57" t="inlineStr">
+      <c r="AN75" s="59" t="inlineStr">
         <is>
           <t>D88</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="AM72" s="57" t="inlineStr">
+    <row r="76">
+      <c r="AM76" s="59" t="inlineStr">
         <is>
           <t>comando_1</t>
         </is>
       </c>
-      <c r="AN72" s="57" t="inlineStr">
+      <c r="AN76" s="59" t="inlineStr">
         <is>
           <t>Z80</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="AM73" s="57" t="inlineStr">
+    <row r="77">
+      <c r="AM77" s="59" t="inlineStr">
         <is>
           <t>comando_2</t>
         </is>
       </c>
-      <c r="AN73" s="57" t="inlineStr">
+      <c r="AN77" s="59" t="inlineStr">
         <is>
           <t>Z81</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="AM74" s="57" t="inlineStr">
+    <row r="78">
+      <c r="AM78" s="59" t="inlineStr">
         <is>
           <t>comando_3</t>
         </is>
       </c>
-      <c r="AN74" s="57" t="inlineStr">
+      <c r="AN78" s="59" t="inlineStr">
         <is>
           <t>Z82</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="AM75" s="57" t="inlineStr">
+    <row r="79">
+      <c r="AM79" s="59" t="inlineStr">
         <is>
           <t>comando_4</t>
         </is>
       </c>
-      <c r="AN75" s="57" t="inlineStr">
+      <c r="AN79" s="59" t="inlineStr">
         <is>
           <t>Z83</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="AM76" s="57" t="inlineStr">
+    <row r="80">
+      <c r="AM80" s="59" t="inlineStr">
         <is>
           <t>comando_5</t>
         </is>
       </c>
-      <c r="AN76" s="57" t="inlineStr">
+      <c r="AN80" s="59" t="inlineStr">
         <is>
           <t>Z84</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="AM77" s="57" t="inlineStr">
+    <row r="81">
+      <c r="AM81" s="59" t="inlineStr">
         <is>
           <t>comando_6</t>
         </is>
       </c>
-      <c r="AN77" s="57" t="inlineStr">
+      <c r="AN81" s="59" t="inlineStr">
         <is>
           <t>Z85</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="AM78" s="57" t="inlineStr">
+    <row r="82">
+      <c r="AM82" s="59" t="inlineStr">
         <is>
           <t>degrau_traco_1</t>
         </is>
       </c>
-      <c r="AN78" s="57" t="inlineStr">
+      <c r="AN82" s="59" t="inlineStr">
         <is>
           <t>O80</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="AM79" s="57" t="inlineStr">
+    <row r="83">
+      <c r="AM83" s="59" t="inlineStr">
         <is>
           <t>degrau_traco_2</t>
         </is>
       </c>
-      <c r="AN79" s="57" t="inlineStr">
+      <c r="AN83" s="59" t="inlineStr">
         <is>
           <t>O81</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="AM80" s="57" t="inlineStr">
+    <row r="84">
+      <c r="AM84" s="59" t="inlineStr">
         <is>
           <t>degrau_traco_3</t>
         </is>
       </c>
-      <c r="AN80" s="57" t="inlineStr">
+      <c r="AN84" s="59" t="inlineStr">
         <is>
           <t>O82</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="AM81" s="57" t="inlineStr">
+    <row r="85">
+      <c r="AM85" s="59" t="inlineStr">
         <is>
           <t>degrau_traco_4</t>
         </is>
       </c>
-      <c r="AN81" s="57" t="inlineStr">
+      <c r="AN85" s="59" t="inlineStr">
         <is>
           <t>O83</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="AM82" s="57" t="inlineStr">
+    <row r="86">
+      <c r="AM86" s="59" t="inlineStr">
         <is>
           <t>degrau_traco_5</t>
         </is>
       </c>
-      <c r="AN82" s="57" t="inlineStr">
+      <c r="AN86" s="59" t="inlineStr">
         <is>
           <t>O84</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="AM83" s="57" t="inlineStr">
+    <row r="87">
+      <c r="AM87" s="59" t="inlineStr">
         <is>
           <t>degrau_traco_6</t>
         </is>
       </c>
-      <c r="AN83" s="57" t="inlineStr">
+      <c r="AN87" s="59" t="inlineStr">
         <is>
           <t>O85</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="AM84" s="57" t="inlineStr">
+    <row r="88">
+      <c r="AM88" s="59" t="inlineStr">
         <is>
           <t>degrau_traco_7</t>
         </is>
       </c>
-      <c r="AN84" s="57" t="inlineStr">
+      <c r="AN88" s="59" t="inlineStr">
         <is>
           <t>O86</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="AM85" s="57" t="inlineStr">
+    <row r="89">
+      <c r="AM89" s="59" t="inlineStr">
         <is>
           <t>degrau_traco_8</t>
         </is>
       </c>
-      <c r="AN85" s="57" t="inlineStr">
+      <c r="AN89" s="59" t="inlineStr">
         <is>
           <t>O87</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="AM86" s="57" t="inlineStr">
+    <row r="90">
+      <c r="AM90" s="59" t="inlineStr">
         <is>
           <t>degrau_traco_9</t>
         </is>
       </c>
-      <c r="AN86" s="57" t="inlineStr">
+      <c r="AN90" s="59" t="inlineStr">
         <is>
           <t>O88</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="AM87" s="57" t="inlineStr">
+    <row r="91">
+      <c r="AM91" s="59" t="inlineStr">
         <is>
           <t>degrau_comando_1</t>
         </is>
       </c>
-      <c r="AN87" s="57" t="inlineStr">
+      <c r="AN91" s="59" t="inlineStr">
         <is>
           <t>AK80</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="AM88" s="57" t="inlineStr">
+    <row r="92">
+      <c r="AM92" s="59" t="inlineStr">
         <is>
           <t>degrau_comando_2</t>
         </is>
       </c>
-      <c r="AN88" s="57" t="inlineStr">
+      <c r="AN92" s="59" t="inlineStr">
         <is>
           <t>AK81</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="AM89" s="57" t="inlineStr">
+    <row r="93">
+      <c r="AM93" s="59" t="inlineStr">
         <is>
           <t>degrau_comando_3</t>
         </is>
       </c>
-      <c r="AN89" s="57" t="inlineStr">
+      <c r="AN93" s="59" t="inlineStr">
         <is>
           <t>AK82</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="AM90" s="57" t="inlineStr">
+    <row r="94">
+      <c r="AM94" s="59" t="inlineStr">
         <is>
           <t>degrau_comando_4</t>
         </is>
       </c>
-      <c r="AN90" s="57" t="inlineStr">
+      <c r="AN94" s="59" t="inlineStr">
         <is>
           <t>AK83</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="AM91" s="57" t="inlineStr">
+    <row r="95">
+      <c r="AM95" s="59" t="inlineStr">
         <is>
           <t>degrau_comando_5</t>
         </is>
       </c>
-      <c r="AN91" s="57" t="inlineStr">
+      <c r="AN95" s="59" t="inlineStr">
         <is>
           <t>AK84</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="AM92" s="57" t="inlineStr">
+    <row r="96">
+      <c r="AM96" s="59" t="inlineStr">
         <is>
           <t>degrau_comando_6</t>
         </is>
       </c>
-      <c r="AN92" s="57" t="inlineStr">
+      <c r="AN96" s="59" t="inlineStr">
         <is>
           <t>AK85</t>
         </is>
